--- a/data/trans_bre/P1803_2016_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1803_2016_2023-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,67</t>
+          <t>-2,28; 1,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,66</t>
+          <t>-0,2; 4,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 57,41</t>
+          <t>-48,31; 70,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 100,95</t>
+          <t>-4,05; 105,51</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-17,16</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-65,51%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,24</t>
+          <t>-1,38; 2,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 2,51</t>
+          <t>-0,6; 4,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 71,26</t>
+          <t>-27,73; 69,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 36,84</t>
+          <t>-8,23; 78,42</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,65</t>
+          <t>-0,41; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,96</t>
+          <t>0,24; 5,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 147,94</t>
+          <t>-13,12; 146,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 62,05</t>
+          <t>1,32; 104,69</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,2</t>
+          <t>-0,65; 4,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,65</t>
+          <t>-2,19; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 84,97</t>
+          <t>-8,82; 81,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 25,02</t>
+          <t>-15,95; 37,25</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-36,46%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,94</t>
+          <t>-0,03; 2,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 1,69</t>
+          <t>0,52; 3,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 48,36</t>
+          <t>-0,54; 53,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 19,99</t>
+          <t>5,72; 45,67</t>
         </is>
       </c>
     </row>
